--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E784A70-5F78-4D0A-899F-513E7D800FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76886E47-2C98-4548-96F2-6AB40AFD1539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26205" yWindow="0" windowWidth="25485" windowHeight="19800" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="9795" yWindow="0" windowWidth="21900" windowHeight="20340" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="22">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -1694,6 +1694,93 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2">
+        <v>46273</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1">
+        <v>100</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="2">
+        <v>46275</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>90</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2">
+        <v>46274</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1">
+        <v>100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I36" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76886E47-2C98-4548-96F2-6AB40AFD1539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE41DFA-82A9-4BF9-9985-56C8C94A23B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9795" yWindow="0" windowWidth="21900" windowHeight="20340" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="20850" yWindow="0" windowWidth="30960" windowHeight="20880" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="22">
   <si>
     <t>Doni Lantow</t>
   </si>
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -1781,6 +1781,180 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="6">
+        <v>46273</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="5">
+        <v>100</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="11">
+        <v>46280</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="10">
+        <v>100</v>
+      </c>
+      <c r="G43" s="12">
+        <v>1</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="6">
+        <v>46282</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="5">
+        <v>60</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="11">
+        <v>46283</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="10">
+        <v>100</v>
+      </c>
+      <c r="G45" s="12">
+        <v>1</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6">
+        <v>46269</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="5">
+        <v>100</v>
+      </c>
+      <c r="G46" s="7">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="11">
+        <v>46280</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="10">
+        <v>100</v>
+      </c>
+      <c r="G47" s="12">
+        <v>1</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="13">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I36" xr:uid="{139554F0-8ABC-4CD8-817E-E6CB5E4FC3E3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/NEW_HIRE_MAS_Scores.xlsx
+++ b/NEW_HIRE_MAS_Scores.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B745B4-2E55-41F5-91E8-448DE3BB7AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="0" windowWidth="30990" windowHeight="20985" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
+    <workbookView xWindow="15255" yWindow="30" windowWidth="36000" windowHeight="20580" xr2:uid="{1898A9E1-10FE-406B-A3BC-4C7125C840EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
